--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.08105675887765</v>
+        <v>2.775671723317618</v>
       </c>
       <c r="D2" t="n">
-        <v>29.69507183174922</v>
+        <v>4.825449172659249</v>
       </c>
       <c r="E2" t="n">
-        <v>4.478107668871392</v>
+        <v>0.727692496191601</v>
       </c>
       <c r="F2" t="n">
-        <v>5.522427625734548</v>
+        <v>0.8973944891818642</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.04311325048144</v>
+        <v>4.069505903203234</v>
       </c>
       <c r="D3" t="n">
-        <v>21.78570601980814</v>
+        <v>3.540177228218822</v>
       </c>
       <c r="E3" t="n">
-        <v>4.478107668871392</v>
+        <v>0.727692496191601</v>
       </c>
       <c r="F3" t="n">
-        <v>5.522427625734548</v>
+        <v>0.8973944891818642</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.6816493546284</v>
+        <v>3.035768020127115</v>
       </c>
       <c r="D4" t="n">
-        <v>15.25120007561805</v>
+        <v>2.478320012287933</v>
       </c>
       <c r="E4" t="n">
-        <v>4.478107668871392</v>
+        <v>0.727692496191601</v>
       </c>
       <c r="F4" t="n">
-        <v>5.522427625734548</v>
+        <v>0.8973944891818642</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.98463506502365</v>
+        <v>1.785003198066344</v>
       </c>
       <c r="D5" t="n">
-        <v>14.39871872866797</v>
+        <v>2.339791793408545</v>
       </c>
       <c r="E5" t="n">
-        <v>4.478107668871392</v>
+        <v>0.727692496191601</v>
       </c>
       <c r="F5" t="n">
-        <v>5.522427625734548</v>
+        <v>0.8973944891818642</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.37820455805674</v>
+        <v>2.98645824068422</v>
       </c>
       <c r="D6" t="n">
-        <v>18.82620723809056</v>
+        <v>3.059258676189716</v>
       </c>
       <c r="E6" t="n">
-        <v>4.478107668871392</v>
+        <v>0.727692496191601</v>
       </c>
       <c r="F6" t="n">
-        <v>5.522427625734548</v>
+        <v>0.8973944891818642</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
